--- a/data/trans_camb/P12_2_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P12_2_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 2,97</t>
+          <t>-7,09; 2,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 0,85</t>
+          <t>-9,13; 0,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 3,26</t>
+          <t>-5,71; 3,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 1,72</t>
+          <t>-11,79; 2,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,05; -6,15</t>
+          <t>-18,58; -6,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,47; -2,7</t>
+          <t>-14,39; -2,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 1,05</t>
+          <t>-7,69; 0,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,47; -3,8</t>
+          <t>-11,69; -3,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 0,01</t>
+          <t>-7,46; -0,12</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 20,68</t>
+          <t>-35,21; 20,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 6,91</t>
+          <t>-45,36; 4,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,04; 23,48</t>
+          <t>-29,78; 26,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 7,65</t>
+          <t>-40,05; 11,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,93; -26,71</t>
+          <t>-62,66; -27,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,21; -13,13</t>
+          <t>-47,65; -12,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 5,55</t>
+          <t>-34,13; 3,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,39; -19,69</t>
+          <t>-49,94; -18,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 0,91</t>
+          <t>-32,9; -0,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 5,7</t>
+          <t>-4,97; 6,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -2,75</t>
+          <t>-13,16; -3,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 1,88</t>
+          <t>-7,85; 2,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 4,12</t>
+          <t>-9,62; 3,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -1,52</t>
+          <t>-13,63; -2,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 2,18</t>
+          <t>-8,9; 2,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 2,88</t>
+          <t>-6,15; 2,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -4,01</t>
+          <t>-11,92; -3,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 0,6</t>
+          <t>-7,51; 0,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,49; 42,03</t>
+          <t>-26,07; 48,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,01; -18,19</t>
+          <t>-68,6; -25,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,85; 13,34</t>
+          <t>-41,28; 15,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 17,84</t>
+          <t>-33,83; 18,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,77; -6,79</t>
+          <t>-49,6; -9,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 10,24</t>
+          <t>-32,07; 9,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 15,75</t>
+          <t>-26,8; 14,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,33; -21,29</t>
+          <t>-52,35; -20,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 3,35</t>
+          <t>-32,1; 1,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 4,62</t>
+          <t>-4,73; 4,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 2,84</t>
+          <t>-6,71; 3,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,18; -0,84</t>
+          <t>-18,33; -0,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 3,33</t>
+          <t>-13,94; 4,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 3,35</t>
+          <t>-16,83; 2,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 7,11</t>
+          <t>-10,41; 6,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 3,1</t>
+          <t>-5,18; 3,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 1,2</t>
+          <t>-7,57; 1,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,05; -0,6</t>
+          <t>-17,8; -0,63</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 26,91</t>
+          <t>-21,62; 29,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 16,41</t>
+          <t>-30,05; 18,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,96; -4,54</t>
+          <t>-79,25; -2,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 13,91</t>
+          <t>-40,28; 22,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,53; 12,67</t>
+          <t>-49,22; 12,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,96; 31,02</t>
+          <t>-31,47; 28,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 16,66</t>
+          <t>-21,92; 15,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 6,29</t>
+          <t>-31,97; 5,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,27; -3,02</t>
+          <t>-71,19; -2,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -1,24</t>
+          <t>-7,95; -0,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,39; -3,04</t>
+          <t>-9,53; -3,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; -0,97</t>
+          <t>-7,96; -1,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 1,19</t>
+          <t>-7,6; 1,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; -1,94</t>
+          <t>-10,36; -2,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,66; -1,11</t>
+          <t>-15,69; -0,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,56; -1,2</t>
+          <t>-6,61; -1,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,95; -3,66</t>
+          <t>-8,75; -3,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,09; -2,17</t>
+          <t>-11,43; -2,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,98; -5,66</t>
+          <t>-31,19; -4,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,85; -13,14</t>
+          <t>-37,47; -13,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,93; -4,06</t>
+          <t>-31,02; -4,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 5,32</t>
+          <t>-28,52; 5,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,65; -8,87</t>
+          <t>-38,63; -9,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,04; -5,0</t>
+          <t>-59,75; -1,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,98; -5,08</t>
+          <t>-26,19; -5,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,1; -15,84</t>
+          <t>-34,44; -16,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,01; -9,92</t>
+          <t>-48,06; -10,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 1,71</t>
+          <t>-9,81; 1,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 4,54</t>
+          <t>-6,32; 4,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 5,86</t>
+          <t>-6,0; 5,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,47</t>
+          <t>-7,11; 3,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 1,66</t>
+          <t>-8,57; 1,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,6; -2,04</t>
+          <t>-15,0; -1,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 0,81</t>
+          <t>-6,84; 0,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,59</t>
+          <t>-6,87; 0,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,51; -0,25</t>
+          <t>-10,04; -0,43</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,43; 8,59</t>
+          <t>-39,27; 9,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 24,99</t>
+          <t>-25,63; 23,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 32,02</t>
+          <t>-24,16; 31,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 12,18</t>
+          <t>-20,45; 12,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 5,34</t>
+          <t>-24,21; 5,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,86; -6,92</t>
+          <t>-42,72; -5,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 3,19</t>
+          <t>-22,5; 2,49</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 2,42</t>
+          <t>-22,33; 2,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-30,88; -1,02</t>
+          <t>-33,39; -2,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 5,04</t>
+          <t>-4,05; 4,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 4,7</t>
+          <t>-3,85; 4,74</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 4,45</t>
+          <t>-5,89; 3,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,32; -2,91</t>
+          <t>-10,37; -2,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -4,57</t>
+          <t>-12,37; -4,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,57; -7,36</t>
+          <t>-14,59; -7,62</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -1,84</t>
+          <t>-8,68; -1,86</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,28; -3,9</t>
+          <t>-10,45; -4,08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,18; -6,8</t>
+          <t>-13,66; -7,03</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,32; 93,36</t>
+          <t>-46,25; 95,8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-44,03; 98,48</t>
+          <t>-44,48; 93,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,82; 91,72</t>
+          <t>-71,38; 98,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,0; -8,86</t>
+          <t>-29,1; -7,28</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,41; -14,47</t>
+          <t>-34,91; -15,05</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-41,34; -22,83</t>
+          <t>-41,08; -23,25</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-28,03; -6,86</t>
+          <t>-28,7; -6,81</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-33,84; -14,51</t>
+          <t>-34,95; -15,18</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-43,67; -25,1</t>
+          <t>-44,8; -24,81</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,27</t>
+          <t>-4,26; -0,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,61; -2,02</t>
+          <t>-5,63; -1,98</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,49; -1,77</t>
+          <t>-7,49; -1,55</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,48; -2,14</t>
+          <t>-6,44; -1,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,49; -5,43</t>
+          <t>-9,53; -5,43</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-12,35; -5,98</t>
+          <t>-12,48; -6,01</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -1,78</t>
+          <t>-4,7; -1,8</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -4,34</t>
+          <t>-7,08; -4,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -4,23</t>
+          <t>-8,79; -4,31</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -1,5</t>
+          <t>-20,73; -0,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-27,6; -10,98</t>
+          <t>-27,52; -10,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,74; -9,44</t>
+          <t>-37,63; -8,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-20,61; -7,14</t>
+          <t>-20,92; -6,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-30,99; -18,94</t>
+          <t>-30,86; -18,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,37; -20,91</t>
+          <t>-42,28; -20,84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,56; -7,45</t>
+          <t>-18,61; -7,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,38; -18,12</t>
+          <t>-27,84; -18,07</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-34,94; -17,68</t>
+          <t>-35,36; -18,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_2_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P12_2_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,49</t>
+          <t>-7,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>-3,67</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 2,97</t>
+          <t>-7,32; 3,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 0,54</t>
+          <t>-8,86; 0,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 3,95</t>
+          <t>-6,12; 3,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 2,15</t>
+          <t>-12,15; 1,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,58; -6,35</t>
+          <t>-19,09; -6,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -2,76</t>
+          <t>-14,32; -2,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 0,58</t>
+          <t>-7,16; 1,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,69; -3,61</t>
+          <t>-11,32; -3,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -0,12</t>
+          <t>-7,46; 0,08</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-6,57%</t>
+          <t>-7,01%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-32,45%</t>
+          <t>-30,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-18,82%</t>
+          <t>-17,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 20,92</t>
+          <t>-36,88; 21,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 4,66</t>
+          <t>-44,46; 6,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 26,5</t>
+          <t>-30,64; 23,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,05; 11,15</t>
+          <t>-40,93; 5,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,66; -27,26</t>
+          <t>-63,62; -26,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,65; -12,69</t>
+          <t>-45,82; -7,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 3,19</t>
+          <t>-31,61; 5,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,94; -18,65</t>
+          <t>-48,97; -17,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,9; -0,54</t>
+          <t>-32,19; 1,17</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,74</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,55</t>
+          <t>-3,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-3,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 6,39</t>
+          <t>-5,39; 6,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -3,69</t>
+          <t>-13,32; -3,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 2,14</t>
+          <t>-8,08; 1,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 3,99</t>
+          <t>-9,39; 4,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,63; -2,07</t>
+          <t>-14,16; -1,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 2,2</t>
+          <t>-9,53; 1,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 2,73</t>
+          <t>-6,08; 2,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,92; -3,94</t>
+          <t>-12,51; -4,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 0,24</t>
+          <t>-7,42; 0,17</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-16,65%</t>
+          <t>-17,82%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-14,23%</t>
+          <t>-14,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-16,86%</t>
+          <t>-17,18%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 48,46</t>
+          <t>-28,26; 44,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,6; -25,78</t>
+          <t>-68,03; -24,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 15,38</t>
+          <t>-42,26; 12,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 18,55</t>
+          <t>-33,28; 17,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,6; -9,13</t>
+          <t>-49,56; -7,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 9,9</t>
+          <t>-33,34; 8,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 14,38</t>
+          <t>-26,26; 14,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,35; -20,55</t>
+          <t>-52,7; -22,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 1,38</t>
+          <t>-31,77; 1,13</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-8,67</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-2,91</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,75</t>
+          <t>-2,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 4,89</t>
+          <t>-5,47; 4,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 3,01</t>
+          <t>-6,74; 2,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,33; -0,69</t>
+          <t>-7,57; 2,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 4,84</t>
+          <t>-13,78; 3,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 2,51</t>
+          <t>-16,4; 2,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 6,52</t>
+          <t>-11,84; 6,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 3,06</t>
+          <t>-5,08; 3,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 1,15</t>
+          <t>-7,58; 0,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,8; -0,63</t>
+          <t>-6,19; 2,51</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-44,2%</t>
+          <t>-12,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-8,32%</t>
+          <t>-10,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-35,64%</t>
+          <t>-9,63%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 29,73</t>
+          <t>-24,46; 24,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 18,07</t>
+          <t>-30,43; 17,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,25; -2,89</t>
+          <t>-33,78; 13,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,28; 22,45</t>
+          <t>-40,24; 16,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,22; 12,13</t>
+          <t>-50,63; 10,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 28,36</t>
+          <t>-34,61; 27,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 15,86</t>
+          <t>-21,3; 15,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,97; 5,91</t>
+          <t>-31,86; 4,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,19; -2,85</t>
+          <t>-26,0; 13,26</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,48</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,85</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,56</t>
+          <t>-3,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,95; -0,84</t>
+          <t>-8,13; -1,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -3,12</t>
+          <t>-9,53; -2,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,96; -1,07</t>
+          <t>-8,12; -1,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 1,2</t>
+          <t>-7,39; 1,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,36; -2,12</t>
+          <t>-10,64; -1,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,69; -0,38</t>
+          <t>-5,11; 2,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; -1,12</t>
+          <t>-6,72; -1,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -3,52</t>
+          <t>-8,95; -3,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,43; -2,36</t>
+          <t>-5,74; -0,49</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-18,85%</t>
+          <t>-20,0%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-28,11%</t>
+          <t>-5,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-23,17%</t>
+          <t>-13,51%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,19; -4,06</t>
+          <t>-31,78; -5,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,47; -13,97</t>
+          <t>-37,67; -13,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -4,91</t>
+          <t>-32,01; -6,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 5,94</t>
+          <t>-28,49; 6,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,63; -9,43</t>
+          <t>-40,03; -8,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,75; -1,8</t>
+          <t>-19,2; 10,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,19; -5,15</t>
+          <t>-26,26; -5,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,44; -16,0</t>
+          <t>-34,96; -16,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,06; -10,76</t>
+          <t>-22,85; -1,95</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-7,05</t>
+          <t>-4,49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,34</t>
+          <t>-3,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 1,44</t>
+          <t>-9,17; 1,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,24</t>
+          <t>-6,4; 4,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 5,8</t>
+          <t>-6,51; 4,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 3,58</t>
+          <t>-7,13; 3,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 1,47</t>
+          <t>-9,18; 1,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,0; -1,35</t>
+          <t>-9,4; -0,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,62</t>
+          <t>-6,59; 0,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 0,75</t>
+          <t>-7,04; 0,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -0,43</t>
+          <t>-7,08; -0,06</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-0,72%</t>
+          <t>-4,95%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-21,7%</t>
+          <t>-13,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,34%</t>
+          <t>-11,94%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 9,51</t>
+          <t>-36,64; 10,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 23,76</t>
+          <t>-25,43; 26,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 31,37</t>
+          <t>-26,34; 27,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 12,11</t>
+          <t>-20,05; 12,68</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 5,0</t>
+          <t>-25,97; 5,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,72; -5,1</t>
+          <t>-25,95; -0,08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 2,49</t>
+          <t>-21,76; 2,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 2,82</t>
+          <t>-22,35; 3,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,39; -2,46</t>
+          <t>-22,82; -0,19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,03</t>
+          <t>-1,53</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-11,06</t>
+          <t>-11,24</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-10,17</t>
+          <t>-9,83</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 4,89</t>
+          <t>-4,01; 4,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 4,74</t>
+          <t>-3,88; 4,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,98</t>
+          <t>-6,05; 3,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,37; -2,37</t>
+          <t>-10,44; -2,39</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,37; -4,83</t>
+          <t>-13,0; -4,87</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,59; -7,62</t>
+          <t>-14,65; -7,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,68; -1,86</t>
+          <t>-8,52; -1,87</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -4,08</t>
+          <t>-10,59; -4,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,66; -7,03</t>
+          <t>-12,85; -6,47</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-29,24%</t>
+          <t>-22,04%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-32,69%</t>
+          <t>-33,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-35,5%</t>
+          <t>-34,3%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,25; 95,8</t>
+          <t>-46,79; 82,07</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-44,48; 93,17</t>
+          <t>-44,53; 93,24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 98,83</t>
+          <t>-69,37; 92,96</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,1; -7,28</t>
+          <t>-29,69; -7,69</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-34,91; -15,05</t>
+          <t>-36,11; -14,73</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-41,08; -23,25</t>
+          <t>-41,58; -22,36</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-28,7; -6,81</t>
+          <t>-28,1; -6,74</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-34,95; -15,18</t>
+          <t>-34,69; -15,57</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-44,8; -24,81</t>
+          <t>-42,54; -23,24</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-2,72</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-8,34</t>
+          <t>-6,31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-6,1</t>
+          <t>-4,51</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,26; -0,18</t>
+          <t>-4,1; -0,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -1,98</t>
+          <t>-6,02; -2,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,49; -1,55</t>
+          <t>-4,59; -0,85</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -1,99</t>
+          <t>-6,71; -2,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -5,43</t>
+          <t>-9,5; -5,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-12,48; -6,01</t>
+          <t>-8,33; -4,31</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,7; -1,8</t>
+          <t>-4,76; -1,82</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -4,27</t>
+          <t>-7,24; -4,36</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,79; -4,31</t>
+          <t>-5,85; -3,11</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-19,76%</t>
+          <t>-13,92%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-28,09%</t>
+          <t>-21,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-24,71%</t>
+          <t>-18,27%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,73; -0,98</t>
+          <t>-19,77; -1,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-27,52; -10,52</t>
+          <t>-28,8; -11,19</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,63; -8,19</t>
+          <t>-22,51; -4,55</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-20,92; -6,79</t>
+          <t>-21,62; -7,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-30,86; -18,84</t>
+          <t>-30,97; -18,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,28; -20,84</t>
+          <t>-26,75; -15,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,61; -7,64</t>
+          <t>-18,55; -7,52</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-27,84; -18,07</t>
+          <t>-28,32; -18,12</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-35,36; -18,13</t>
+          <t>-22,87; -13,0</t>
         </is>
       </c>
     </row>
